--- a/data.xlsx
+++ b/data.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11003"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="129" documentId="11_4AB480A97D773D78B6F332151CC35944F734729B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26F37891-402D-454B-AC02-39E6E12760EF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{394ACB00-0539-ED43-AEA5-843A3569C8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="135" windowWidth="21075" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="21080" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="9">
   <si>
     <t>Angle (degrees)</t>
   </si>
@@ -66,10 +66,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -95,8 +102,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,16 +409,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G121"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G181"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -433,7 +441,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>120</v>
       </c>
@@ -457,7 +465,7 @@
         <v>33.783783800000002</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>120</v>
       </c>
@@ -481,7 +489,7 @@
         <v>28.1879195</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>120</v>
       </c>
@@ -505,7 +513,7 @@
         <v>31.555555600000002</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>120</v>
       </c>
@@ -529,7 +537,7 @@
         <v>31.617647099999999</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>120</v>
       </c>
@@ -553,7 +561,7 @@
         <v>34.589041100000003</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>120</v>
       </c>
@@ -577,7 +585,7 @@
         <v>28.9198606</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>120</v>
       </c>
@@ -601,7 +609,7 @@
         <v>27.972028000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>120</v>
       </c>
@@ -625,7 +633,7 @@
         <v>33.802816900000003</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>120</v>
       </c>
@@ -649,7 +657,7 @@
         <v>33.018867899999996</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>120</v>
       </c>
@@ -673,7 +681,7 @@
         <v>44.108761299999998</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>120</v>
       </c>
@@ -697,7 +705,7 @@
         <v>26.168224299999999</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>120</v>
       </c>
@@ -721,7 +729,7 @@
         <v>26.599326600000001</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>120</v>
       </c>
@@ -745,7 +753,7 @@
         <v>24.2937853</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>120</v>
       </c>
@@ -769,7 +777,7 @@
         <v>21.846153900000001</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>120</v>
       </c>
@@ -793,7 +801,7 @@
         <v>22.0994475</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>120</v>
       </c>
@@ -817,7 +825,7 @@
         <v>27.444794999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>120</v>
       </c>
@@ -841,7 +849,7 @@
         <v>19.676549900000001</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>120</v>
       </c>
@@ -865,7 +873,7 @@
         <v>26.4084507</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>120</v>
       </c>
@@ -889,7 +897,7 @@
         <v>29.299363100000001</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>120</v>
       </c>
@@ -913,7 +921,7 @@
         <v>22.686567199999999</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>120</v>
       </c>
@@ -937,7 +945,7 @@
         <v>23.8970588</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>120</v>
       </c>
@@ -961,7 +969,7 @@
         <v>21.180555600000002</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>120</v>
       </c>
@@ -985,7 +993,7 @@
         <v>17.3758865</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>120</v>
       </c>
@@ -1009,7 +1017,7 @@
         <v>27.935222700000001</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>120</v>
       </c>
@@ -1033,7 +1041,7 @@
         <v>21.7054264</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>120</v>
       </c>
@@ -1057,7 +1065,7 @@
         <v>26.859504099999999</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>120</v>
       </c>
@@ -1081,7 +1089,7 @@
         <v>24.675324700000001</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>120</v>
       </c>
@@ -1105,7 +1113,7 @@
         <v>17.2284644</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>120</v>
       </c>
@@ -1129,7 +1137,7 @@
         <v>20.3883495</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>120</v>
       </c>
@@ -1153,7 +1161,7 @@
         <v>16.6666667</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>120</v>
       </c>
@@ -1177,7 +1185,7 @@
         <v>12.169309999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>120</v>
       </c>
@@ -1201,7 +1209,7 @@
         <v>14.19753</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>120</v>
       </c>
@@ -1225,7 +1233,7 @@
         <v>16.556290000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>120</v>
       </c>
@@ -1249,7 +1257,7 @@
         <v>17.770029999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>120</v>
       </c>
@@ -1273,7 +1281,7 @@
         <v>20.538720000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>120</v>
       </c>
@@ -1297,7 +1305,7 @@
         <v>23.75</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>120</v>
       </c>
@@ -1321,7 +1329,7 @@
         <v>19.615379999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>120</v>
       </c>
@@ -1345,7 +1353,7 @@
         <v>19.463090000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>120</v>
       </c>
@@ -1369,7 +1377,7 @@
         <v>18.12689</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>120</v>
       </c>
@@ -1393,7 +1401,7 @@
         <v>26.141079999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>120</v>
       </c>
@@ -1417,7 +1425,7 @@
         <v>66.486490000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>120</v>
       </c>
@@ -1441,7 +1449,7 @@
         <v>52.140079999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>120</v>
       </c>
@@ -1465,7 +1473,7 @@
         <v>68.273089999999996</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>120</v>
       </c>
@@ -1489,7 +1497,7 @@
         <v>61.904760000000003</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>120</v>
       </c>
@@ -1513,7 +1521,7 @@
         <v>70.0565</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>120</v>
       </c>
@@ -1537,7 +1545,7 @@
         <v>71.495329999999996</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>120</v>
       </c>
@@ -1561,7 +1569,7 @@
         <v>58.22222</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>120</v>
       </c>
@@ -1585,7 +1593,7 @@
         <v>59.130429999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>120</v>
       </c>
@@ -1609,7 +1617,7 @@
         <v>57.312249999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>120</v>
       </c>
@@ -1633,7 +1641,7 @@
         <v>53.284669999999998</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>120</v>
       </c>
@@ -1657,7 +1665,7 @@
         <v>51.489359999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>120</v>
       </c>
@@ -1681,7 +1689,7 @@
         <v>44.366199999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>120</v>
       </c>
@@ -1705,7 +1713,7 @@
         <v>55.263159999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>120</v>
       </c>
@@ -1729,7 +1737,7 @@
         <v>46.792450000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>120</v>
       </c>
@@ -1753,7 +1761,7 @@
         <v>49.158250000000002</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>120</v>
       </c>
@@ -1777,7 +1785,7 @@
         <v>52.398519999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>120</v>
       </c>
@@ -1801,7 +1809,7 @@
         <v>49.799199999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>120</v>
       </c>
@@ -1825,7 +1833,7 @@
         <v>47.692309999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>120</v>
       </c>
@@ -1849,7 +1857,7 @@
         <v>53.284669999999998</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>120</v>
       </c>
@@ -1873,7 +1881,7 @@
         <v>52.416359999999997</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>120</v>
       </c>
@@ -1897,7 +1905,7 @@
         <v>65.044250000000005</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>120</v>
       </c>
@@ -1921,7 +1929,7 @@
         <v>57.731960000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>120</v>
       </c>
@@ -1945,7 +1953,7 @@
         <v>66.375550000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>120</v>
       </c>
@@ -1969,7 +1977,7 @@
         <v>53.115729999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>120</v>
       </c>
@@ -1993,7 +2001,7 @@
         <v>60.638300000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>120</v>
       </c>
@@ -2017,7 +2025,7 @@
         <v>63.272730000000003</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>120</v>
       </c>
@@ -2041,7 +2049,7 @@
         <v>53.424660000000003</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>120</v>
       </c>
@@ -2065,7 +2073,7 @@
         <v>56.074770000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>120</v>
       </c>
@@ -2089,7 +2097,7 @@
         <v>55.700330000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>120</v>
       </c>
@@ -2113,7 +2121,7 @@
         <v>60.383389999999999</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>120</v>
       </c>
@@ -2137,7 +2145,7 @@
         <v>41.724139999999998</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>120</v>
       </c>
@@ -2161,7 +2169,7 @@
         <v>34.177219999999998</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>120</v>
       </c>
@@ -2185,7 +2193,7 @@
         <v>31.85379</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>120</v>
       </c>
@@ -2209,7 +2217,7 @@
         <v>38.590600000000002</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>120</v>
       </c>
@@ -2233,7 +2241,7 @@
         <v>38.596490000000003</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>120</v>
       </c>
@@ -2257,7 +2265,7 @@
         <v>45.744680000000002</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>120</v>
       </c>
@@ -2281,7 +2289,7 @@
         <v>46.551720000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>120</v>
       </c>
@@ -2305,7 +2313,7 @@
         <v>44.736840000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>120</v>
       </c>
@@ -2329,7 +2337,7 @@
         <v>38.225259999999999</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>120</v>
       </c>
@@ -2353,7 +2361,7 @@
         <v>38.181820000000002</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>60</v>
       </c>
@@ -2377,7 +2385,7 @@
         <v>36.448599999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>60</v>
       </c>
@@ -2401,7 +2409,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>60</v>
       </c>
@@ -2425,7 +2433,7 @@
         <v>42.622950799999998</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>60</v>
       </c>
@@ -2449,7 +2457,7 @@
         <v>41.836730000000003</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>60</v>
       </c>
@@ -2473,7 +2481,7 @@
         <v>37.121209999999998</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>60</v>
       </c>
@@ -2497,7 +2505,7 @@
         <v>40.601500000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>60</v>
       </c>
@@ -2521,7 +2529,7 @@
         <v>39.552239999999998</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>60</v>
       </c>
@@ -2545,7 +2553,7 @@
         <v>38.461539999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>60</v>
       </c>
@@ -2569,7 +2577,7 @@
         <v>45.744680000000002</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>60</v>
       </c>
@@ -2593,7 +2601,7 @@
         <v>41.836730000000003</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>60</v>
       </c>
@@ -2617,7 +2625,7 @@
         <v>32.82443</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>60</v>
       </c>
@@ -2641,7 +2649,7 @@
         <v>40.384619999999998</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>60</v>
       </c>
@@ -2665,7 +2673,7 @@
         <v>38.970588200000002</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>60</v>
       </c>
@@ -2689,7 +2697,7 @@
         <v>34.883719999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>60</v>
       </c>
@@ -2713,7 +2721,7 @@
         <v>35.526319999999998</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>60</v>
       </c>
@@ -2737,7 +2745,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>60</v>
       </c>
@@ -2761,7 +2769,7 @@
         <v>37.142859999999999</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>60</v>
       </c>
@@ -2785,7 +2793,7 @@
         <v>36.538460000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>60</v>
       </c>
@@ -2809,7 +2817,7 @@
         <v>39.130429999999997</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>60</v>
       </c>
@@ -2833,7 +2841,7 @@
         <v>40.425530000000002</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>60</v>
       </c>
@@ -2857,7 +2865,7 @@
         <v>11.32075</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>60</v>
       </c>
@@ -2881,7 +2889,7 @@
         <v>12.59843</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>60</v>
       </c>
@@ -2905,7 +2913,7 @@
         <v>10.169491499999999</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>60</v>
       </c>
@@ -2929,7 +2937,7 @@
         <v>9.5238099999999992</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>60</v>
       </c>
@@ -2953,7 +2961,7 @@
         <v>11.57025</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>60</v>
       </c>
@@ -2964,7 +2972,7 @@
         <v>3</v>
       </c>
       <c r="D107">
-        <f t="shared" ref="D107:D121" si="2">B107/C107</f>
+        <f t="shared" ref="D107:D170" si="2">B107/C107</f>
         <v>1.3333333333333333</v>
       </c>
       <c r="E107" t="s">
@@ -2977,7 +2985,7 @@
         <v>10.294119999999999</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>60</v>
       </c>
@@ -3001,7 +3009,7 @@
         <v>11.50442</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>60</v>
       </c>
@@ -3025,7 +3033,7 @@
         <v>12.38095</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>60</v>
       </c>
@@ -3049,7 +3057,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>60</v>
       </c>
@@ -3073,7 +3081,7 @@
         <v>11.304349999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>60</v>
       </c>
@@ -3097,7 +3105,7 @@
         <v>8.9108909999999995</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>60</v>
       </c>
@@ -3121,7 +3129,7 @@
         <v>6.7961169999999997</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>60</v>
       </c>
@@ -3145,7 +3153,7 @@
         <v>9.80392157</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>60</v>
       </c>
@@ -3169,7 +3177,7 @@
         <v>8.9285709999999998</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>60</v>
       </c>
@@ -3193,7 +3201,7 @@
         <v>9.0909089999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>60</v>
       </c>
@@ -3217,7 +3225,7 @@
         <v>9.4594590000000007</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>60</v>
       </c>
@@ -3241,7 +3249,7 @@
         <v>9.0909089999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>60</v>
       </c>
@@ -3265,7 +3273,7 @@
         <v>11.764709999999999</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>60</v>
       </c>
@@ -3289,7 +3297,7 @@
         <v>8.0808079999999993</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>60</v>
       </c>
@@ -3311,6 +3319,1446 @@
       </c>
       <c r="G121">
         <v>9.5238099999999992</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>60</v>
+      </c>
+      <c r="B122">
+        <v>4</v>
+      </c>
+      <c r="C122">
+        <v>3.5</v>
+      </c>
+      <c r="D122">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E122" t="s">
+        <v>7</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122" s="1">
+        <v>52.763820000000003</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>60</v>
+      </c>
+      <c r="B123">
+        <v>4</v>
+      </c>
+      <c r="C123">
+        <v>3.5</v>
+      </c>
+      <c r="D123">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E123" t="s">
+        <v>7</v>
+      </c>
+      <c r="F123">
+        <v>2</v>
+      </c>
+      <c r="G123">
+        <v>47.342995169082123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>60</v>
+      </c>
+      <c r="B124">
+        <v>4</v>
+      </c>
+      <c r="C124">
+        <v>3.5</v>
+      </c>
+      <c r="D124">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E124" t="s">
+        <v>7</v>
+      </c>
+      <c r="F124">
+        <v>3</v>
+      </c>
+      <c r="G124">
+        <v>52.941176470588239</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>60</v>
+      </c>
+      <c r="B125">
+        <v>4</v>
+      </c>
+      <c r="C125">
+        <v>3.5</v>
+      </c>
+      <c r="D125">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E125" t="s">
+        <v>7</v>
+      </c>
+      <c r="F125">
+        <v>4</v>
+      </c>
+      <c r="G125">
+        <v>50.24154589371981</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>60</v>
+      </c>
+      <c r="B126">
+        <v>4</v>
+      </c>
+      <c r="C126">
+        <v>3.5</v>
+      </c>
+      <c r="D126">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E126" t="s">
+        <v>7</v>
+      </c>
+      <c r="F126">
+        <v>5</v>
+      </c>
+      <c r="G126">
+        <v>51.832460732984295</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>60</v>
+      </c>
+      <c r="B127">
+        <v>4</v>
+      </c>
+      <c r="C127">
+        <v>3.5</v>
+      </c>
+      <c r="D127">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E127" t="s">
+        <v>7</v>
+      </c>
+      <c r="F127">
+        <v>6</v>
+      </c>
+      <c r="G127">
+        <v>50.259067357512954</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>60</v>
+      </c>
+      <c r="B128">
+        <v>4</v>
+      </c>
+      <c r="C128">
+        <v>3.5</v>
+      </c>
+      <c r="D128">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E128" t="s">
+        <v>7</v>
+      </c>
+      <c r="F128">
+        <v>7</v>
+      </c>
+      <c r="G128">
+        <v>47.945205479452049</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>60</v>
+      </c>
+      <c r="B129">
+        <v>4</v>
+      </c>
+      <c r="C129">
+        <v>3.5</v>
+      </c>
+      <c r="D129">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E129" t="s">
+        <v>7</v>
+      </c>
+      <c r="F129">
+        <v>8</v>
+      </c>
+      <c r="G129">
+        <v>50.232558139534888</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>60</v>
+      </c>
+      <c r="B130">
+        <v>4</v>
+      </c>
+      <c r="C130">
+        <v>3.5</v>
+      </c>
+      <c r="D130">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E130" t="s">
+        <v>7</v>
+      </c>
+      <c r="F130">
+        <v>9</v>
+      </c>
+      <c r="G130">
+        <v>49.743589743589745</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>60</v>
+      </c>
+      <c r="B131">
+        <v>4</v>
+      </c>
+      <c r="C131">
+        <v>3.5</v>
+      </c>
+      <c r="D131">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E131" t="s">
+        <v>7</v>
+      </c>
+      <c r="F131">
+        <v>10</v>
+      </c>
+      <c r="G131">
+        <v>45.851528384279476</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>60</v>
+      </c>
+      <c r="B132">
+        <v>4</v>
+      </c>
+      <c r="C132">
+        <v>3.5</v>
+      </c>
+      <c r="D132">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E132" t="s">
+        <v>8</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="G132">
+        <v>50.505050505050505</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>60</v>
+      </c>
+      <c r="B133">
+        <v>4</v>
+      </c>
+      <c r="C133">
+        <v>3.5</v>
+      </c>
+      <c r="D133">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E133" t="s">
+        <v>8</v>
+      </c>
+      <c r="F133">
+        <v>2</v>
+      </c>
+      <c r="G133">
+        <v>41.935483870967744</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>60</v>
+      </c>
+      <c r="B134">
+        <v>4</v>
+      </c>
+      <c r="C134">
+        <v>3.5</v>
+      </c>
+      <c r="D134">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E134" t="s">
+        <v>8</v>
+      </c>
+      <c r="F134">
+        <v>3</v>
+      </c>
+      <c r="G134">
+        <v>41.32231404958678</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>60</v>
+      </c>
+      <c r="B135">
+        <v>4</v>
+      </c>
+      <c r="C135">
+        <v>3.5</v>
+      </c>
+      <c r="D135">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E135" t="s">
+        <v>8</v>
+      </c>
+      <c r="F135">
+        <v>4</v>
+      </c>
+      <c r="G135">
+        <v>41.148325358851672</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>60</v>
+      </c>
+      <c r="B136">
+        <v>4</v>
+      </c>
+      <c r="C136">
+        <v>3.5</v>
+      </c>
+      <c r="D136">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E136" t="s">
+        <v>8</v>
+      </c>
+      <c r="F136">
+        <v>5</v>
+      </c>
+      <c r="G136">
+        <v>46.632124352331608</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>60</v>
+      </c>
+      <c r="B137">
+        <v>4</v>
+      </c>
+      <c r="C137">
+        <v>3.5</v>
+      </c>
+      <c r="D137">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E137" t="s">
+        <v>8</v>
+      </c>
+      <c r="F137">
+        <v>6</v>
+      </c>
+      <c r="G137">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>60</v>
+      </c>
+      <c r="B138">
+        <v>4</v>
+      </c>
+      <c r="C138">
+        <v>3.5</v>
+      </c>
+      <c r="D138">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E138" t="s">
+        <v>8</v>
+      </c>
+      <c r="F138">
+        <v>7</v>
+      </c>
+      <c r="G138">
+        <v>42.424242424242422</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>60</v>
+      </c>
+      <c r="B139">
+        <v>4</v>
+      </c>
+      <c r="C139">
+        <v>3.5</v>
+      </c>
+      <c r="D139">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E139" t="s">
+        <v>8</v>
+      </c>
+      <c r="F139">
+        <v>8</v>
+      </c>
+      <c r="G139">
+        <v>46.188340807174889</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>60</v>
+      </c>
+      <c r="B140">
+        <v>4</v>
+      </c>
+      <c r="C140">
+        <v>3.5</v>
+      </c>
+      <c r="D140">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E140" t="s">
+        <v>8</v>
+      </c>
+      <c r="F140">
+        <v>9</v>
+      </c>
+      <c r="G140">
+        <v>47.422680412371129</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>60</v>
+      </c>
+      <c r="B141">
+        <v>4</v>
+      </c>
+      <c r="C141">
+        <v>3.5</v>
+      </c>
+      <c r="D141">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E141" t="s">
+        <v>8</v>
+      </c>
+      <c r="F141">
+        <v>10</v>
+      </c>
+      <c r="G141">
+        <v>41.255605381165921</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>90</v>
+      </c>
+      <c r="B142">
+        <v>4</v>
+      </c>
+      <c r="C142">
+        <v>4</v>
+      </c>
+      <c r="D142">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E142" t="s">
+        <v>7</v>
+      </c>
+      <c r="F142">
+        <v>1</v>
+      </c>
+      <c r="G142">
+        <v>70.897832817337459</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>90</v>
+      </c>
+      <c r="B143">
+        <v>4</v>
+      </c>
+      <c r="C143">
+        <v>4</v>
+      </c>
+      <c r="D143">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E143" t="s">
+        <v>7</v>
+      </c>
+      <c r="F143">
+        <v>2</v>
+      </c>
+      <c r="G143">
+        <v>79.591836734693871</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>90</v>
+      </c>
+      <c r="B144">
+        <v>4</v>
+      </c>
+      <c r="C144">
+        <v>4</v>
+      </c>
+      <c r="D144">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E144" t="s">
+        <v>7</v>
+      </c>
+      <c r="F144">
+        <v>3</v>
+      </c>
+      <c r="G144">
+        <v>69.25373134328359</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>90</v>
+      </c>
+      <c r="B145">
+        <v>4</v>
+      </c>
+      <c r="C145">
+        <v>4</v>
+      </c>
+      <c r="D145">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E145" t="s">
+        <v>7</v>
+      </c>
+      <c r="F145">
+        <v>4</v>
+      </c>
+      <c r="G145">
+        <v>76.071428571428569</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>90</v>
+      </c>
+      <c r="B146">
+        <v>4</v>
+      </c>
+      <c r="C146">
+        <v>4</v>
+      </c>
+      <c r="D146">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E146" t="s">
+        <v>7</v>
+      </c>
+      <c r="F146">
+        <v>5</v>
+      </c>
+      <c r="G146">
+        <v>72.834645669291348</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>90</v>
+      </c>
+      <c r="B147">
+        <v>4</v>
+      </c>
+      <c r="C147">
+        <v>4</v>
+      </c>
+      <c r="D147">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E147" t="s">
+        <v>7</v>
+      </c>
+      <c r="F147">
+        <v>6</v>
+      </c>
+      <c r="G147">
+        <v>74.909090909090921</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>90</v>
+      </c>
+      <c r="B148">
+        <v>4</v>
+      </c>
+      <c r="C148">
+        <v>4</v>
+      </c>
+      <c r="D148">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E148" t="s">
+        <v>7</v>
+      </c>
+      <c r="F148">
+        <v>7</v>
+      </c>
+      <c r="G148">
+        <v>71.181556195965427</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>90</v>
+      </c>
+      <c r="B149">
+        <v>4</v>
+      </c>
+      <c r="C149">
+        <v>4</v>
+      </c>
+      <c r="D149">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E149" t="s">
+        <v>7</v>
+      </c>
+      <c r="F149">
+        <v>8</v>
+      </c>
+      <c r="G149">
+        <v>81.311475409836063</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>90</v>
+      </c>
+      <c r="B150">
+        <v>4</v>
+      </c>
+      <c r="C150">
+        <v>4</v>
+      </c>
+      <c r="D150">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E150" t="s">
+        <v>7</v>
+      </c>
+      <c r="F150">
+        <v>9</v>
+      </c>
+      <c r="G150">
+        <v>78.742514970059887</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>90</v>
+      </c>
+      <c r="B151">
+        <v>4</v>
+      </c>
+      <c r="C151">
+        <v>4</v>
+      </c>
+      <c r="D151">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E151" t="s">
+        <v>7</v>
+      </c>
+      <c r="F151">
+        <v>10</v>
+      </c>
+      <c r="G151">
+        <v>69.732937685459945</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>90</v>
+      </c>
+      <c r="B152">
+        <v>4</v>
+      </c>
+      <c r="C152">
+        <v>4</v>
+      </c>
+      <c r="D152">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E152" t="s">
+        <v>8</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="G152">
+        <v>57.875457875457883</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>90</v>
+      </c>
+      <c r="B153">
+        <v>4</v>
+      </c>
+      <c r="C153">
+        <v>4</v>
+      </c>
+      <c r="D153">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E153" t="s">
+        <v>8</v>
+      </c>
+      <c r="F153">
+        <v>2</v>
+      </c>
+      <c r="G153">
+        <v>52.996845425867512</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>90</v>
+      </c>
+      <c r="B154">
+        <v>4</v>
+      </c>
+      <c r="C154">
+        <v>4</v>
+      </c>
+      <c r="D154">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E154" t="s">
+        <v>8</v>
+      </c>
+      <c r="F154">
+        <v>3</v>
+      </c>
+      <c r="G154">
+        <v>50.803858520900327</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>90</v>
+      </c>
+      <c r="B155">
+        <v>4</v>
+      </c>
+      <c r="C155">
+        <v>4</v>
+      </c>
+      <c r="D155">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E155" t="s">
+        <v>8</v>
+      </c>
+      <c r="F155">
+        <v>4</v>
+      </c>
+      <c r="G155">
+        <v>56.856187290969892</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>90</v>
+      </c>
+      <c r="B156">
+        <v>4</v>
+      </c>
+      <c r="C156">
+        <v>4</v>
+      </c>
+      <c r="D156">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E156" t="s">
+        <v>8</v>
+      </c>
+      <c r="F156">
+        <v>5</v>
+      </c>
+      <c r="G156">
+        <v>55.805243445692888</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>90</v>
+      </c>
+      <c r="B157">
+        <v>4</v>
+      </c>
+      <c r="C157">
+        <v>4</v>
+      </c>
+      <c r="D157">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E157" t="s">
+        <v>8</v>
+      </c>
+      <c r="F157">
+        <v>6</v>
+      </c>
+      <c r="G157">
+        <v>59.259259259259252</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>90</v>
+      </c>
+      <c r="B158">
+        <v>4</v>
+      </c>
+      <c r="C158">
+        <v>4</v>
+      </c>
+      <c r="D158">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E158" t="s">
+        <v>8</v>
+      </c>
+      <c r="F158">
+        <v>7</v>
+      </c>
+      <c r="G158">
+        <v>51.677852348993291</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>90</v>
+      </c>
+      <c r="B159">
+        <v>4</v>
+      </c>
+      <c r="C159">
+        <v>4</v>
+      </c>
+      <c r="D159">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E159" t="s">
+        <v>8</v>
+      </c>
+      <c r="F159">
+        <v>8</v>
+      </c>
+      <c r="G159">
+        <v>54.895104895104893</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>90</v>
+      </c>
+      <c r="B160">
+        <v>4</v>
+      </c>
+      <c r="C160">
+        <v>4</v>
+      </c>
+      <c r="D160">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E160" t="s">
+        <v>8</v>
+      </c>
+      <c r="F160">
+        <v>9</v>
+      </c>
+      <c r="G160">
+        <v>61.904761904761905</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>90</v>
+      </c>
+      <c r="B161">
+        <v>4</v>
+      </c>
+      <c r="C161">
+        <v>4</v>
+      </c>
+      <c r="D161">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E161" t="s">
+        <v>8</v>
+      </c>
+      <c r="F161">
+        <v>10</v>
+      </c>
+      <c r="G161">
+        <v>59.696969696969695</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>90</v>
+      </c>
+      <c r="B162">
+        <v>4</v>
+      </c>
+      <c r="C162">
+        <v>3.5</v>
+      </c>
+      <c r="D162">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E162" t="s">
+        <v>7</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="G162">
+        <v>51.821862348178136</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>90</v>
+      </c>
+      <c r="B163">
+        <v>4</v>
+      </c>
+      <c r="C163">
+        <v>3.5</v>
+      </c>
+      <c r="D163">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E163" t="s">
+        <v>7</v>
+      </c>
+      <c r="F163">
+        <v>2</v>
+      </c>
+      <c r="G163">
+        <v>62.272727272727266</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>90</v>
+      </c>
+      <c r="B164">
+        <v>4</v>
+      </c>
+      <c r="C164">
+        <v>3.5</v>
+      </c>
+      <c r="D164">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E164" t="s">
+        <v>7</v>
+      </c>
+      <c r="F164">
+        <v>3</v>
+      </c>
+      <c r="G164">
+        <v>50.925925925925931</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>90</v>
+      </c>
+      <c r="B165">
+        <v>4</v>
+      </c>
+      <c r="C165">
+        <v>3.5</v>
+      </c>
+      <c r="D165">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E165" t="s">
+        <v>7</v>
+      </c>
+      <c r="F165">
+        <v>4</v>
+      </c>
+      <c r="G165">
+        <v>69.543147208121823</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>90</v>
+      </c>
+      <c r="B166">
+        <v>4</v>
+      </c>
+      <c r="C166">
+        <v>3.5</v>
+      </c>
+      <c r="D166">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E166" t="s">
+        <v>7</v>
+      </c>
+      <c r="F166">
+        <v>5</v>
+      </c>
+      <c r="G166">
+        <v>83.568075117370881</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>90</v>
+      </c>
+      <c r="B167">
+        <v>4</v>
+      </c>
+      <c r="C167">
+        <v>3.5</v>
+      </c>
+      <c r="D167">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E167" t="s">
+        <v>7</v>
+      </c>
+      <c r="F167">
+        <v>6</v>
+      </c>
+      <c r="G167">
+        <v>53.879310344827594</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>90</v>
+      </c>
+      <c r="B168">
+        <v>4</v>
+      </c>
+      <c r="C168">
+        <v>3.5</v>
+      </c>
+      <c r="D168">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E168" t="s">
+        <v>7</v>
+      </c>
+      <c r="F168">
+        <v>7</v>
+      </c>
+      <c r="G168">
+        <v>55.066079295154182</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>90</v>
+      </c>
+      <c r="B169">
+        <v>4</v>
+      </c>
+      <c r="C169">
+        <v>3.5</v>
+      </c>
+      <c r="D169">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E169" t="s">
+        <v>7</v>
+      </c>
+      <c r="F169">
+        <v>8</v>
+      </c>
+      <c r="G169">
+        <v>46.938775510204081</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>90</v>
+      </c>
+      <c r="B170">
+        <v>4</v>
+      </c>
+      <c r="C170">
+        <v>3.5</v>
+      </c>
+      <c r="D170">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E170" t="s">
+        <v>7</v>
+      </c>
+      <c r="F170">
+        <v>9</v>
+      </c>
+      <c r="G170">
+        <v>43.61702127659575</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>90</v>
+      </c>
+      <c r="B171">
+        <v>4</v>
+      </c>
+      <c r="C171">
+        <v>3.5</v>
+      </c>
+      <c r="D171">
+        <f t="shared" ref="D171:D181" si="3">B171/C171</f>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E171" t="s">
+        <v>7</v>
+      </c>
+      <c r="F171">
+        <v>10</v>
+      </c>
+      <c r="G171">
+        <v>54.296875</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>90</v>
+      </c>
+      <c r="B172">
+        <v>4</v>
+      </c>
+      <c r="C172">
+        <v>3.5</v>
+      </c>
+      <c r="D172">
+        <f t="shared" si="3"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E172" t="s">
+        <v>8</v>
+      </c>
+      <c r="F172">
+        <v>1</v>
+      </c>
+      <c r="G172">
+        <v>44.363636363636367</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>90</v>
+      </c>
+      <c r="B173">
+        <v>4</v>
+      </c>
+      <c r="C173">
+        <v>3.5</v>
+      </c>
+      <c r="D173">
+        <f t="shared" si="3"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E173" t="s">
+        <v>8</v>
+      </c>
+      <c r="F173">
+        <v>2</v>
+      </c>
+      <c r="G173">
+        <v>42.361111111111107</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>90</v>
+      </c>
+      <c r="B174">
+        <v>4</v>
+      </c>
+      <c r="C174">
+        <v>3.5</v>
+      </c>
+      <c r="D174">
+        <f t="shared" si="3"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E174" t="s">
+        <v>8</v>
+      </c>
+      <c r="F174">
+        <v>3</v>
+      </c>
+      <c r="G174">
+        <v>46.206896551724135</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>90</v>
+      </c>
+      <c r="B175">
+        <v>4</v>
+      </c>
+      <c r="C175">
+        <v>3.5</v>
+      </c>
+      <c r="D175">
+        <f t="shared" si="3"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E175" t="s">
+        <v>8</v>
+      </c>
+      <c r="F175">
+        <v>4</v>
+      </c>
+      <c r="G175">
+        <v>53.556485355648533</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>90</v>
+      </c>
+      <c r="B176">
+        <v>4</v>
+      </c>
+      <c r="C176">
+        <v>3.5</v>
+      </c>
+      <c r="D176">
+        <f t="shared" si="3"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E176" t="s">
+        <v>8</v>
+      </c>
+      <c r="F176">
+        <v>5</v>
+      </c>
+      <c r="G176">
+        <v>56.521739130434781</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>90</v>
+      </c>
+      <c r="B177">
+        <v>4</v>
+      </c>
+      <c r="C177">
+        <v>3.5</v>
+      </c>
+      <c r="D177">
+        <f t="shared" si="3"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E177" t="s">
+        <v>8</v>
+      </c>
+      <c r="F177">
+        <v>6</v>
+      </c>
+      <c r="G177">
+        <v>38.650306748466257</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>90</v>
+      </c>
+      <c r="B178">
+        <v>4</v>
+      </c>
+      <c r="C178">
+        <v>3.5</v>
+      </c>
+      <c r="D178">
+        <f t="shared" si="3"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E178" t="s">
+        <v>8</v>
+      </c>
+      <c r="F178">
+        <v>7</v>
+      </c>
+      <c r="G178">
+        <v>47.199999999999996</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>90</v>
+      </c>
+      <c r="B179">
+        <v>4</v>
+      </c>
+      <c r="C179">
+        <v>3.5</v>
+      </c>
+      <c r="D179">
+        <f t="shared" si="3"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E179" t="s">
+        <v>8</v>
+      </c>
+      <c r="F179">
+        <v>8</v>
+      </c>
+      <c r="G179">
+        <v>42.857142857142854</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>90</v>
+      </c>
+      <c r="B180">
+        <v>4</v>
+      </c>
+      <c r="C180">
+        <v>3.5</v>
+      </c>
+      <c r="D180">
+        <f t="shared" si="3"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E180" t="s">
+        <v>8</v>
+      </c>
+      <c r="F180">
+        <v>9</v>
+      </c>
+      <c r="G180">
+        <v>41.275167785234899</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>90</v>
+      </c>
+      <c r="B181">
+        <v>4</v>
+      </c>
+      <c r="C181">
+        <v>3.5</v>
+      </c>
+      <c r="D181">
+        <f t="shared" si="3"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="E181" t="s">
+        <v>8</v>
+      </c>
+      <c r="F181">
+        <v>10</v>
+      </c>
+      <c r="G181">
+        <v>36.148648648648653</v>
       </c>
     </row>
   </sheetData>
@@ -3322,7 +4770,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3332,7 +4780,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11003"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{394ACB00-0539-ED43-AEA5-843A3569C8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{244E1A94-8795-A541-AE8C-5F1783F90DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="21080" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13440" yWindow="500" windowWidth="14720" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="9">
   <si>
     <t>Angle (degrees)</t>
   </si>
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
@@ -4508,7 +4508,7 @@
         <v>3.5</v>
       </c>
       <c r="D171">
-        <f t="shared" ref="D171:D181" si="3">B171/C171</f>
+        <f t="shared" ref="D171:D201" si="3">B171/C171</f>
         <v>1.1428571428571428</v>
       </c>
       <c r="E171" t="s">
@@ -4759,6 +4759,486 @@
       </c>
       <c r="G181">
         <v>36.148648648648653</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>90</v>
+      </c>
+      <c r="B182">
+        <v>4</v>
+      </c>
+      <c r="C182">
+        <v>3</v>
+      </c>
+      <c r="D182">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E182" t="s">
+        <v>7</v>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182">
+        <v>12.71186</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>90</v>
+      </c>
+      <c r="B183">
+        <v>4</v>
+      </c>
+      <c r="C183">
+        <v>3</v>
+      </c>
+      <c r="D183">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E183" t="s">
+        <v>7</v>
+      </c>
+      <c r="F183">
+        <v>2</v>
+      </c>
+      <c r="G183">
+        <v>62.272730000000003</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>90</v>
+      </c>
+      <c r="B184">
+        <v>4</v>
+      </c>
+      <c r="C184">
+        <v>3</v>
+      </c>
+      <c r="D184">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E184" t="s">
+        <v>7</v>
+      </c>
+      <c r="F184">
+        <v>3</v>
+      </c>
+      <c r="G184">
+        <v>50.925930000000001</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>90</v>
+      </c>
+      <c r="B185">
+        <v>4</v>
+      </c>
+      <c r="C185">
+        <v>3</v>
+      </c>
+      <c r="D185">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E185" t="s">
+        <v>7</v>
+      </c>
+      <c r="F185">
+        <v>4</v>
+      </c>
+      <c r="G185">
+        <v>69.543149999999997</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>90</v>
+      </c>
+      <c r="B186">
+        <v>4</v>
+      </c>
+      <c r="C186">
+        <v>3</v>
+      </c>
+      <c r="D186">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E186" t="s">
+        <v>7</v>
+      </c>
+      <c r="F186">
+        <v>5</v>
+      </c>
+      <c r="G186">
+        <v>83.568079999999995</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>90</v>
+      </c>
+      <c r="B187">
+        <v>4</v>
+      </c>
+      <c r="C187">
+        <v>3</v>
+      </c>
+      <c r="D187">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E187" t="s">
+        <v>7</v>
+      </c>
+      <c r="F187">
+        <v>6</v>
+      </c>
+      <c r="G187">
+        <v>53.879309999999997</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>90</v>
+      </c>
+      <c r="B188">
+        <v>4</v>
+      </c>
+      <c r="C188">
+        <v>3</v>
+      </c>
+      <c r="D188">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E188" t="s">
+        <v>7</v>
+      </c>
+      <c r="F188">
+        <v>7</v>
+      </c>
+      <c r="G188">
+        <v>55.066079999999999</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>90</v>
+      </c>
+      <c r="B189">
+        <v>4</v>
+      </c>
+      <c r="C189">
+        <v>3</v>
+      </c>
+      <c r="D189">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E189" t="s">
+        <v>7</v>
+      </c>
+      <c r="F189">
+        <v>8</v>
+      </c>
+      <c r="G189">
+        <v>46.938780000000001</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>90</v>
+      </c>
+      <c r="B190">
+        <v>4</v>
+      </c>
+      <c r="C190">
+        <v>3</v>
+      </c>
+      <c r="D190">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E190" t="s">
+        <v>7</v>
+      </c>
+      <c r="F190">
+        <v>9</v>
+      </c>
+      <c r="G190">
+        <v>43.617019999999997</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>90</v>
+      </c>
+      <c r="B191">
+        <v>4</v>
+      </c>
+      <c r="C191">
+        <v>3</v>
+      </c>
+      <c r="D191">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E191" t="s">
+        <v>7</v>
+      </c>
+      <c r="F191">
+        <v>10</v>
+      </c>
+      <c r="G191">
+        <v>54.296880000000002</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>90</v>
+      </c>
+      <c r="B192">
+        <v>4</v>
+      </c>
+      <c r="C192">
+        <v>3</v>
+      </c>
+      <c r="D192">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E192" t="s">
+        <v>8</v>
+      </c>
+      <c r="F192">
+        <v>1</v>
+      </c>
+      <c r="G192">
+        <v>11.71875</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>90</v>
+      </c>
+      <c r="B193">
+        <v>4</v>
+      </c>
+      <c r="C193">
+        <v>3</v>
+      </c>
+      <c r="D193">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E193" t="s">
+        <v>8</v>
+      </c>
+      <c r="F193">
+        <v>2</v>
+      </c>
+      <c r="G193">
+        <v>42.361109999999996</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>90</v>
+      </c>
+      <c r="B194">
+        <v>4</v>
+      </c>
+      <c r="C194">
+        <v>3</v>
+      </c>
+      <c r="D194">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E194" t="s">
+        <v>8</v>
+      </c>
+      <c r="F194">
+        <v>3</v>
+      </c>
+      <c r="G194">
+        <v>46.206899999999997</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>90</v>
+      </c>
+      <c r="B195">
+        <v>4</v>
+      </c>
+      <c r="C195">
+        <v>3</v>
+      </c>
+      <c r="D195">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E195" t="s">
+        <v>8</v>
+      </c>
+      <c r="F195">
+        <v>4</v>
+      </c>
+      <c r="G195">
+        <v>53.556489999999997</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>90</v>
+      </c>
+      <c r="B196">
+        <v>4</v>
+      </c>
+      <c r="C196">
+        <v>3</v>
+      </c>
+      <c r="D196">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E196" t="s">
+        <v>8</v>
+      </c>
+      <c r="F196">
+        <v>5</v>
+      </c>
+      <c r="G196">
+        <v>56.521740000000001</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>90</v>
+      </c>
+      <c r="B197">
+        <v>4</v>
+      </c>
+      <c r="C197">
+        <v>3</v>
+      </c>
+      <c r="D197">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E197" t="s">
+        <v>8</v>
+      </c>
+      <c r="F197">
+        <v>6</v>
+      </c>
+      <c r="G197">
+        <v>38.650309999999998</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>90</v>
+      </c>
+      <c r="B198">
+        <v>4</v>
+      </c>
+      <c r="C198">
+        <v>3</v>
+      </c>
+      <c r="D198">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E198" t="s">
+        <v>8</v>
+      </c>
+      <c r="F198">
+        <v>7</v>
+      </c>
+      <c r="G198">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>90</v>
+      </c>
+      <c r="B199">
+        <v>4</v>
+      </c>
+      <c r="C199">
+        <v>3</v>
+      </c>
+      <c r="D199">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E199" t="s">
+        <v>8</v>
+      </c>
+      <c r="F199">
+        <v>8</v>
+      </c>
+      <c r="G199">
+        <v>42.857140000000001</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A200">
+        <v>90</v>
+      </c>
+      <c r="B200">
+        <v>4</v>
+      </c>
+      <c r="C200">
+        <v>3</v>
+      </c>
+      <c r="D200">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E200" t="s">
+        <v>8</v>
+      </c>
+      <c r="F200">
+        <v>9</v>
+      </c>
+      <c r="G200">
+        <v>41.275170000000003</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A201">
+        <v>90</v>
+      </c>
+      <c r="B201">
+        <v>4</v>
+      </c>
+      <c r="C201">
+        <v>3</v>
+      </c>
+      <c r="D201">
+        <f t="shared" si="3"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E201" t="s">
+        <v>8</v>
+      </c>
+      <c r="F201">
+        <v>10</v>
+      </c>
+      <c r="G201">
+        <v>36.148650000000004</v>
       </c>
     </row>
   </sheetData>
